--- a/MoneyKeel/documents/other/moneykeel_calc_plan_launch-readiness_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_launch-readiness_v01.xlsx
@@ -37,7 +37,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FAEEDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DFF2E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,22 +72,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -713,7 +705,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Net worth 55 of 77 · Cash flow 25 of 42 · Performance 24 of 31 — 104 decisions have nothing that re-runs them</t>
+          <t>Net worth 53 of 78 · Cash flow 25 of 42 · Performance 23 of 33 — 101 decisions have nothing that re-runs them</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -741,14 +733,14 @@
           <t>Claude</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>DONE</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>formula-agreement PASS · rulings-in-file PASS · rulings-sync PASS · changelog-anchored PASS · read-from-approved PASS</t>
+          <t>formula-agreement FAIL · rulings-in-file PASS · rulings-sync PASS · changelog-anchored PASS · read-from-approved PASS</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -771,7 +763,7 @@
           <t>Answer the open questions</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>FOUNDER</t>
         </is>
@@ -783,7 +775,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Net worth 14 on figures + 5 on decisions · Cash flow 0 on figures + 2 on decisions · Performance 1 on figures + 4 on decisions — 26 open</t>
+          <t>Net worth 13 on figures + 5 on decisions · Cash flow 0 on figures + 2 on decisions · Performance 0 on figures + 4 on decisions — 24 open</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -806,7 +798,7 @@
           <t>Read every row and mark it VERIFIED, or say what is wrong</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>FOUNDER</t>
         </is>
@@ -841,7 +833,7 @@
           <t>Pre-build checklist presented, and your explicit "cut the build"</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Claude to present · FOUNDER to say</t>
         </is>
